--- a/testing/glm-mv-reference/spss-output/mv5_two_way.xlsx
+++ b/testing/glm-mv-reference/spss-output/mv5_two_way.xlsx
@@ -1147,99 +1147,99 @@
   </cellXfs>
   <cellStyles count="94">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="style1790153343577" xfId="1"/>
-    <cellStyle name="style1790153343606" xfId="2"/>
-    <cellStyle name="style1790153343628" xfId="3"/>
-    <cellStyle name="style1790153343658" xfId="4"/>
-    <cellStyle name="style1790153343679" xfId="5"/>
-    <cellStyle name="style1790153343700" xfId="6"/>
-    <cellStyle name="style1790153343718" xfId="7"/>
-    <cellStyle name="style1790153343743" xfId="8"/>
-    <cellStyle name="style1790153343763" xfId="9"/>
-    <cellStyle name="style1790153343787" xfId="10"/>
-    <cellStyle name="style1790153343811" xfId="11"/>
-    <cellStyle name="style1790153343833" xfId="12"/>
-    <cellStyle name="style1790153343854" xfId="13"/>
-    <cellStyle name="style1790153343876" xfId="14"/>
-    <cellStyle name="style1790153343898" xfId="15"/>
-    <cellStyle name="style1790153343912" xfId="16"/>
-    <cellStyle name="style1790153343926" xfId="17"/>
-    <cellStyle name="style1790153343947" xfId="18"/>
-    <cellStyle name="style1790153343967" xfId="19"/>
-    <cellStyle name="style1790153343987" xfId="20"/>
-    <cellStyle name="style1790153344007" xfId="21"/>
-    <cellStyle name="style1790153344028" xfId="22"/>
-    <cellStyle name="style1790153344043" xfId="23"/>
-    <cellStyle name="style1790153344051" xfId="24"/>
-    <cellStyle name="style1790153344074" xfId="25"/>
-    <cellStyle name="style1790153344094" xfId="26"/>
-    <cellStyle name="style1790153344113" xfId="27"/>
-    <cellStyle name="style1790153344134" xfId="28"/>
-    <cellStyle name="style1790153344155" xfId="29"/>
-    <cellStyle name="style1790153344175" xfId="30"/>
-    <cellStyle name="style1790153344198" xfId="31"/>
-    <cellStyle name="style1790153344215" xfId="32"/>
-    <cellStyle name="style1790153344239" xfId="33"/>
-    <cellStyle name="style1790153344252" xfId="34"/>
-    <cellStyle name="style1790153344282" xfId="35"/>
-    <cellStyle name="style1790153344301" xfId="36"/>
-    <cellStyle name="style1790153344321" xfId="37"/>
-    <cellStyle name="style1790153344341" xfId="38"/>
-    <cellStyle name="style1790153344362" xfId="39"/>
-    <cellStyle name="style1790153344381" xfId="40"/>
-    <cellStyle name="style1790153344405" xfId="41"/>
-    <cellStyle name="style1790153344423" xfId="42"/>
-    <cellStyle name="style1790153344434" xfId="43"/>
-    <cellStyle name="style1790153344454" xfId="44"/>
-    <cellStyle name="style1790153344468" xfId="45"/>
-    <cellStyle name="style1790153344489" xfId="46"/>
-    <cellStyle name="style1790153344507" xfId="47"/>
-    <cellStyle name="style1790153344526" xfId="48"/>
-    <cellStyle name="style1790153344545" xfId="49"/>
-    <cellStyle name="style1790153344560" xfId="50"/>
-    <cellStyle name="style1790153344573" xfId="51"/>
-    <cellStyle name="style1790153344590" xfId="52"/>
-    <cellStyle name="style1790153344603" xfId="53"/>
-    <cellStyle name="style1790153344616" xfId="54"/>
-    <cellStyle name="style1790153344637" xfId="55"/>
-    <cellStyle name="style1790153344651" xfId="56"/>
-    <cellStyle name="style1790153344666" xfId="57"/>
-    <cellStyle name="style1790153344679" xfId="58"/>
-    <cellStyle name="style1790153344690" xfId="59"/>
-    <cellStyle name="style1790153344707" xfId="60"/>
-    <cellStyle name="style1790153344719" xfId="61"/>
-    <cellStyle name="style1790153344739" xfId="62"/>
-    <cellStyle name="style1790153344758" xfId="63"/>
-    <cellStyle name="style1790153344772" xfId="64"/>
-    <cellStyle name="style1790153344791" xfId="65"/>
-    <cellStyle name="style1790153344811" xfId="66"/>
-    <cellStyle name="style1790153344830" xfId="67"/>
-    <cellStyle name="style1790153344848" xfId="68"/>
-    <cellStyle name="style1790153344860" xfId="69"/>
-    <cellStyle name="style1790153344874" xfId="70"/>
-    <cellStyle name="style1790153344888" xfId="71"/>
-    <cellStyle name="style1790153344902" xfId="72"/>
-    <cellStyle name="style1790153344918" xfId="73"/>
-    <cellStyle name="style1790153344931" xfId="74"/>
-    <cellStyle name="style1790153344944" xfId="75"/>
-    <cellStyle name="style1790153344951" xfId="76"/>
-    <cellStyle name="style1790153344976" xfId="77"/>
-    <cellStyle name="style1790153344990" xfId="78"/>
-    <cellStyle name="style1790153345002" xfId="79"/>
-    <cellStyle name="style1790153345017" xfId="80"/>
-    <cellStyle name="style1790153345038" xfId="81"/>
-    <cellStyle name="style1790153345053" xfId="82"/>
-    <cellStyle name="style1790153345068" xfId="83"/>
-    <cellStyle name="style1790153345084" xfId="84"/>
-    <cellStyle name="style1790153345097" xfId="85"/>
-    <cellStyle name="style1790153345121" xfId="86"/>
-    <cellStyle name="style1790153345137" xfId="87"/>
-    <cellStyle name="style1790153345154" xfId="88"/>
-    <cellStyle name="style1790153345168" xfId="89"/>
-    <cellStyle name="style1790153345185" xfId="90"/>
-    <cellStyle name="style1790153345200" xfId="91"/>
-    <cellStyle name="style1790153345215" xfId="92"/>
-    <cellStyle name="style1790153345228" xfId="93"/>
+    <cellStyle name="style1791033987604" xfId="1"/>
+    <cellStyle name="style1791033987666" xfId="2"/>
+    <cellStyle name="style1791033987686" xfId="3"/>
+    <cellStyle name="style1791033987721" xfId="4"/>
+    <cellStyle name="style1791033987756" xfId="5"/>
+    <cellStyle name="style1791033987786" xfId="6"/>
+    <cellStyle name="style1791033987810" xfId="7"/>
+    <cellStyle name="style1791033987839" xfId="8"/>
+    <cellStyle name="style1791033987866" xfId="9"/>
+    <cellStyle name="style1791033987896" xfId="10"/>
+    <cellStyle name="style1791033987926" xfId="11"/>
+    <cellStyle name="style1791033987956" xfId="12"/>
+    <cellStyle name="style1791033987984" xfId="13"/>
+    <cellStyle name="style1791033988016" xfId="14"/>
+    <cellStyle name="style1791033988041" xfId="15"/>
+    <cellStyle name="style1791033988068" xfId="16"/>
+    <cellStyle name="style1791033988089" xfId="17"/>
+    <cellStyle name="style1791033988117" xfId="18"/>
+    <cellStyle name="style1791033988146" xfId="19"/>
+    <cellStyle name="style1791033988173" xfId="20"/>
+    <cellStyle name="style1791033988198" xfId="21"/>
+    <cellStyle name="style1791033988224" xfId="22"/>
+    <cellStyle name="style1791033988240" xfId="23"/>
+    <cellStyle name="style1791033988261" xfId="24"/>
+    <cellStyle name="style1791033988281" xfId="25"/>
+    <cellStyle name="style1791033988306" xfId="26"/>
+    <cellStyle name="style1791033988330" xfId="27"/>
+    <cellStyle name="style1791033988356" xfId="28"/>
+    <cellStyle name="style1791033988378" xfId="29"/>
+    <cellStyle name="style1791033988406" xfId="30"/>
+    <cellStyle name="style1791033988431" xfId="31"/>
+    <cellStyle name="style1791033988458" xfId="32"/>
+    <cellStyle name="style1791033988486" xfId="33"/>
+    <cellStyle name="style1791033988510" xfId="34"/>
+    <cellStyle name="style1791033988538" xfId="35"/>
+    <cellStyle name="style1791033988562" xfId="36"/>
+    <cellStyle name="style1791033988584" xfId="37"/>
+    <cellStyle name="style1791033988609" xfId="38"/>
+    <cellStyle name="style1791033988634" xfId="39"/>
+    <cellStyle name="style1791033988656" xfId="40"/>
+    <cellStyle name="style1791033988691" xfId="41"/>
+    <cellStyle name="style1791033988716" xfId="42"/>
+    <cellStyle name="style1791033988731" xfId="43"/>
+    <cellStyle name="style1791033988758" xfId="44"/>
+    <cellStyle name="style1791033988778" xfId="45"/>
+    <cellStyle name="style1791033988805" xfId="46"/>
+    <cellStyle name="style1791033988830" xfId="47"/>
+    <cellStyle name="style1791033988856" xfId="48"/>
+    <cellStyle name="style1791033988883" xfId="49"/>
+    <cellStyle name="style1791033988899" xfId="50"/>
+    <cellStyle name="style1791033988919" xfId="51"/>
+    <cellStyle name="style1791033988940" xfId="52"/>
+    <cellStyle name="style1791033988956" xfId="53"/>
+    <cellStyle name="style1791033988976" xfId="54"/>
+    <cellStyle name="style1791033989001" xfId="55"/>
+    <cellStyle name="style1791033989016" xfId="56"/>
+    <cellStyle name="style1791033989044" xfId="57"/>
+    <cellStyle name="style1791033989056" xfId="58"/>
+    <cellStyle name="style1791033989081" xfId="59"/>
+    <cellStyle name="style1791033989102" xfId="60"/>
+    <cellStyle name="style1791033989126" xfId="61"/>
+    <cellStyle name="style1791033989150" xfId="62"/>
+    <cellStyle name="style1791033989171" xfId="63"/>
+    <cellStyle name="style1791033989190" xfId="64"/>
+    <cellStyle name="style1791033989216" xfId="65"/>
+    <cellStyle name="style1791033989240" xfId="66"/>
+    <cellStyle name="style1791033989266" xfId="67"/>
+    <cellStyle name="style1791033989286" xfId="68"/>
+    <cellStyle name="style1791033989304" xfId="69"/>
+    <cellStyle name="style1791033989316" xfId="70"/>
+    <cellStyle name="style1791033989336" xfId="71"/>
+    <cellStyle name="style1791033989355" xfId="72"/>
+    <cellStyle name="style1791033989371" xfId="73"/>
+    <cellStyle name="style1791033989389" xfId="74"/>
+    <cellStyle name="style1791033989407" xfId="75"/>
+    <cellStyle name="style1791033989421" xfId="76"/>
+    <cellStyle name="style1791033989449" xfId="77"/>
+    <cellStyle name="style1791033989471" xfId="78"/>
+    <cellStyle name="style1791033989491" xfId="79"/>
+    <cellStyle name="style1791033989511" xfId="80"/>
+    <cellStyle name="style1791033989543" xfId="81"/>
+    <cellStyle name="style1791033989563" xfId="82"/>
+    <cellStyle name="style1791033989582" xfId="83"/>
+    <cellStyle name="style1791033989603" xfId="84"/>
+    <cellStyle name="style1791033989624" xfId="85"/>
+    <cellStyle name="style1791033989651" xfId="86"/>
+    <cellStyle name="style1791033989666" xfId="87"/>
+    <cellStyle name="style1791033989691" xfId="88"/>
+    <cellStyle name="style1791033989706" xfId="89"/>
+    <cellStyle name="style1791033989726" xfId="90"/>
+    <cellStyle name="style1791033989743" xfId="91"/>
+    <cellStyle name="style1791033989757" xfId="92"/>
+    <cellStyle name="style1791033989779" xfId="93"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1644,7 +1644,7 @@
       <c r="B18" s="8"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>23-SEP-2026 15:49:03</t>
+          <t>03-OCT-2026 20:26:27</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>00:00:00.02</t>
+          <t>00:00:00.00</t>
         </is>
       </c>
     </row>

--- a/testing/glm-mv-reference/spss-output/mv5_two_way.xlsx
+++ b/testing/glm-mv-reference/spss-output/mv5_two_way.xlsx
@@ -1147,99 +1147,99 @@
   </cellXfs>
   <cellStyles count="94">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="style1791033987604" xfId="1"/>
-    <cellStyle name="style1791033987666" xfId="2"/>
-    <cellStyle name="style1791033987686" xfId="3"/>
-    <cellStyle name="style1791033987721" xfId="4"/>
-    <cellStyle name="style1791033987756" xfId="5"/>
-    <cellStyle name="style1791033987786" xfId="6"/>
-    <cellStyle name="style1791033987810" xfId="7"/>
-    <cellStyle name="style1791033987839" xfId="8"/>
-    <cellStyle name="style1791033987866" xfId="9"/>
-    <cellStyle name="style1791033987896" xfId="10"/>
-    <cellStyle name="style1791033987926" xfId="11"/>
-    <cellStyle name="style1791033987956" xfId="12"/>
-    <cellStyle name="style1791033987984" xfId="13"/>
-    <cellStyle name="style1791033988016" xfId="14"/>
-    <cellStyle name="style1791033988041" xfId="15"/>
-    <cellStyle name="style1791033988068" xfId="16"/>
-    <cellStyle name="style1791033988089" xfId="17"/>
-    <cellStyle name="style1791033988117" xfId="18"/>
-    <cellStyle name="style1791033988146" xfId="19"/>
-    <cellStyle name="style1791033988173" xfId="20"/>
-    <cellStyle name="style1791033988198" xfId="21"/>
-    <cellStyle name="style1791033988224" xfId="22"/>
-    <cellStyle name="style1791033988240" xfId="23"/>
-    <cellStyle name="style1791033988261" xfId="24"/>
-    <cellStyle name="style1791033988281" xfId="25"/>
-    <cellStyle name="style1791033988306" xfId="26"/>
-    <cellStyle name="style1791033988330" xfId="27"/>
-    <cellStyle name="style1791033988356" xfId="28"/>
-    <cellStyle name="style1791033988378" xfId="29"/>
-    <cellStyle name="style1791033988406" xfId="30"/>
-    <cellStyle name="style1791033988431" xfId="31"/>
-    <cellStyle name="style1791033988458" xfId="32"/>
-    <cellStyle name="style1791033988486" xfId="33"/>
-    <cellStyle name="style1791033988510" xfId="34"/>
-    <cellStyle name="style1791033988538" xfId="35"/>
-    <cellStyle name="style1791033988562" xfId="36"/>
-    <cellStyle name="style1791033988584" xfId="37"/>
-    <cellStyle name="style1791033988609" xfId="38"/>
-    <cellStyle name="style1791033988634" xfId="39"/>
-    <cellStyle name="style1791033988656" xfId="40"/>
-    <cellStyle name="style1791033988691" xfId="41"/>
-    <cellStyle name="style1791033988716" xfId="42"/>
-    <cellStyle name="style1791033988731" xfId="43"/>
-    <cellStyle name="style1791033988758" xfId="44"/>
-    <cellStyle name="style1791033988778" xfId="45"/>
-    <cellStyle name="style1791033988805" xfId="46"/>
-    <cellStyle name="style1791033988830" xfId="47"/>
-    <cellStyle name="style1791033988856" xfId="48"/>
-    <cellStyle name="style1791033988883" xfId="49"/>
-    <cellStyle name="style1791033988899" xfId="50"/>
-    <cellStyle name="style1791033988919" xfId="51"/>
-    <cellStyle name="style1791033988940" xfId="52"/>
-    <cellStyle name="style1791033988956" xfId="53"/>
-    <cellStyle name="style1791033988976" xfId="54"/>
-    <cellStyle name="style1791033989001" xfId="55"/>
-    <cellStyle name="style1791033989016" xfId="56"/>
-    <cellStyle name="style1791033989044" xfId="57"/>
-    <cellStyle name="style1791033989056" xfId="58"/>
-    <cellStyle name="style1791033989081" xfId="59"/>
-    <cellStyle name="style1791033989102" xfId="60"/>
-    <cellStyle name="style1791033989126" xfId="61"/>
-    <cellStyle name="style1791033989150" xfId="62"/>
-    <cellStyle name="style1791033989171" xfId="63"/>
-    <cellStyle name="style1791033989190" xfId="64"/>
-    <cellStyle name="style1791033989216" xfId="65"/>
-    <cellStyle name="style1791033989240" xfId="66"/>
-    <cellStyle name="style1791033989266" xfId="67"/>
-    <cellStyle name="style1791033989286" xfId="68"/>
-    <cellStyle name="style1791033989304" xfId="69"/>
-    <cellStyle name="style1791033989316" xfId="70"/>
-    <cellStyle name="style1791033989336" xfId="71"/>
-    <cellStyle name="style1791033989355" xfId="72"/>
-    <cellStyle name="style1791033989371" xfId="73"/>
-    <cellStyle name="style1791033989389" xfId="74"/>
-    <cellStyle name="style1791033989407" xfId="75"/>
-    <cellStyle name="style1791033989421" xfId="76"/>
-    <cellStyle name="style1791033989449" xfId="77"/>
-    <cellStyle name="style1791033989471" xfId="78"/>
-    <cellStyle name="style1791033989491" xfId="79"/>
-    <cellStyle name="style1791033989511" xfId="80"/>
-    <cellStyle name="style1791033989543" xfId="81"/>
-    <cellStyle name="style1791033989563" xfId="82"/>
-    <cellStyle name="style1791033989582" xfId="83"/>
-    <cellStyle name="style1791033989603" xfId="84"/>
-    <cellStyle name="style1791033989624" xfId="85"/>
-    <cellStyle name="style1791033989651" xfId="86"/>
-    <cellStyle name="style1791033989666" xfId="87"/>
-    <cellStyle name="style1791033989691" xfId="88"/>
-    <cellStyle name="style1791033989706" xfId="89"/>
-    <cellStyle name="style1791033989726" xfId="90"/>
-    <cellStyle name="style1791033989743" xfId="91"/>
-    <cellStyle name="style1791033989757" xfId="92"/>
-    <cellStyle name="style1791033989779" xfId="93"/>
+    <cellStyle name="style1790153343577" xfId="1"/>
+    <cellStyle name="style1790153343606" xfId="2"/>
+    <cellStyle name="style1790153343628" xfId="3"/>
+    <cellStyle name="style1790153343658" xfId="4"/>
+    <cellStyle name="style1790153343679" xfId="5"/>
+    <cellStyle name="style1790153343700" xfId="6"/>
+    <cellStyle name="style1790153343718" xfId="7"/>
+    <cellStyle name="style1790153343743" xfId="8"/>
+    <cellStyle name="style1790153343763" xfId="9"/>
+    <cellStyle name="style1790153343787" xfId="10"/>
+    <cellStyle name="style1790153343811" xfId="11"/>
+    <cellStyle name="style1790153343833" xfId="12"/>
+    <cellStyle name="style1790153343854" xfId="13"/>
+    <cellStyle name="style1790153343876" xfId="14"/>
+    <cellStyle name="style1790153343898" xfId="15"/>
+    <cellStyle name="style1790153343912" xfId="16"/>
+    <cellStyle name="style1790153343926" xfId="17"/>
+    <cellStyle name="style1790153343947" xfId="18"/>
+    <cellStyle name="style1790153343967" xfId="19"/>
+    <cellStyle name="style1790153343987" xfId="20"/>
+    <cellStyle name="style1790153344007" xfId="21"/>
+    <cellStyle name="style1790153344028" xfId="22"/>
+    <cellStyle name="style1790153344043" xfId="23"/>
+    <cellStyle name="style1790153344051" xfId="24"/>
+    <cellStyle name="style1790153344074" xfId="25"/>
+    <cellStyle name="style1790153344094" xfId="26"/>
+    <cellStyle name="style1790153344113" xfId="27"/>
+    <cellStyle name="style1790153344134" xfId="28"/>
+    <cellStyle name="style1790153344155" xfId="29"/>
+    <cellStyle name="style1790153344175" xfId="30"/>
+    <cellStyle name="style1790153344198" xfId="31"/>
+    <cellStyle name="style1790153344215" xfId="32"/>
+    <cellStyle name="style1790153344239" xfId="33"/>
+    <cellStyle name="style1790153344252" xfId="34"/>
+    <cellStyle name="style1790153344282" xfId="35"/>
+    <cellStyle name="style1790153344301" xfId="36"/>
+    <cellStyle name="style1790153344321" xfId="37"/>
+    <cellStyle name="style1790153344341" xfId="38"/>
+    <cellStyle name="style1790153344362" xfId="39"/>
+    <cellStyle name="style1790153344381" xfId="40"/>
+    <cellStyle name="style1790153344405" xfId="41"/>
+    <cellStyle name="style1790153344423" xfId="42"/>
+    <cellStyle name="style1790153344434" xfId="43"/>
+    <cellStyle name="style1790153344454" xfId="44"/>
+    <cellStyle name="style1790153344468" xfId="45"/>
+    <cellStyle name="style1790153344489" xfId="46"/>
+    <cellStyle name="style1790153344507" xfId="47"/>
+    <cellStyle name="style1790153344526" xfId="48"/>
+    <cellStyle name="style1790153344545" xfId="49"/>
+    <cellStyle name="style1790153344560" xfId="50"/>
+    <cellStyle name="style1790153344573" xfId="51"/>
+    <cellStyle name="style1790153344590" xfId="52"/>
+    <cellStyle name="style1790153344603" xfId="53"/>
+    <cellStyle name="style1790153344616" xfId="54"/>
+    <cellStyle name="style1790153344637" xfId="55"/>
+    <cellStyle name="style1790153344651" xfId="56"/>
+    <cellStyle name="style1790153344666" xfId="57"/>
+    <cellStyle name="style1790153344679" xfId="58"/>
+    <cellStyle name="style1790153344690" xfId="59"/>
+    <cellStyle name="style1790153344707" xfId="60"/>
+    <cellStyle name="style1790153344719" xfId="61"/>
+    <cellStyle name="style1790153344739" xfId="62"/>
+    <cellStyle name="style1790153344758" xfId="63"/>
+    <cellStyle name="style1790153344772" xfId="64"/>
+    <cellStyle name="style1790153344791" xfId="65"/>
+    <cellStyle name="style1790153344811" xfId="66"/>
+    <cellStyle name="style1790153344830" xfId="67"/>
+    <cellStyle name="style1790153344848" xfId="68"/>
+    <cellStyle name="style1790153344860" xfId="69"/>
+    <cellStyle name="style1790153344874" xfId="70"/>
+    <cellStyle name="style1790153344888" xfId="71"/>
+    <cellStyle name="style1790153344902" xfId="72"/>
+    <cellStyle name="style1790153344918" xfId="73"/>
+    <cellStyle name="style1790153344931" xfId="74"/>
+    <cellStyle name="style1790153344944" xfId="75"/>
+    <cellStyle name="style1790153344951" xfId="76"/>
+    <cellStyle name="style1790153344976" xfId="77"/>
+    <cellStyle name="style1790153344990" xfId="78"/>
+    <cellStyle name="style1790153345002" xfId="79"/>
+    <cellStyle name="style1790153345017" xfId="80"/>
+    <cellStyle name="style1790153345038" xfId="81"/>
+    <cellStyle name="style1790153345053" xfId="82"/>
+    <cellStyle name="style1790153345068" xfId="83"/>
+    <cellStyle name="style1790153345084" xfId="84"/>
+    <cellStyle name="style1790153345097" xfId="85"/>
+    <cellStyle name="style1790153345121" xfId="86"/>
+    <cellStyle name="style1790153345137" xfId="87"/>
+    <cellStyle name="style1790153345154" xfId="88"/>
+    <cellStyle name="style1790153345168" xfId="89"/>
+    <cellStyle name="style1790153345185" xfId="90"/>
+    <cellStyle name="style1790153345200" xfId="91"/>
+    <cellStyle name="style1790153345215" xfId="92"/>
+    <cellStyle name="style1790153345228" xfId="93"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1644,7 +1644,7 @@
       <c r="B18" s="8"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>03-OCT-2026 20:26:27</t>
+          <t>23-SEP-2026 15:49:03</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>00:00:00.00</t>
+          <t>00:00:00.02</t>
         </is>
       </c>
     </row>
